--- a/media/imports/purchase_orders/po_template.xlsx
+++ b/media/imports/purchase_orders/po_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sbadmin\sbadmin\store_admin\static\import_templates\purchase_orders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46E0EBE-B421-48FC-B33D-EC2309B3F4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263FF86B-8036-4A54-B3E9-6622F74CD29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1FA050CB-7431-474B-835C-839E53BEE716}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="58">
   <si>
     <t>Vendor Name</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>po2</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>13/1/2026</t>
   </si>
 </sst>
 </file>
@@ -294,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -335,6 +341,7 @@
     <xf numFmtId="8" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -858,6 +865,9 @@
         <v>999108</v>
       </c>
       <c r="K3" s="4"/>
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
       <c r="Q3" s="4" t="s">
         <v>38</v>
       </c>
@@ -909,6 +919,9 @@
         <v>999108</v>
       </c>
       <c r="K4" s="4"/>
+      <c r="M4" s="16">
+        <v>46357</v>
+      </c>
       <c r="Q4" s="4" t="s">
         <v>39</v>
       </c>
@@ -960,6 +973,9 @@
         <v>999108</v>
       </c>
       <c r="K5" s="4"/>
+      <c r="L5" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="Q5" s="4" t="s">
         <v>40</v>
       </c>
@@ -1011,6 +1027,9 @@
         <v>999108</v>
       </c>
       <c r="K6" s="4"/>
+      <c r="M6" s="16">
+        <v>46357</v>
+      </c>
       <c r="Q6" s="4" t="s">
         <v>28</v>
       </c>
@@ -1164,6 +1183,9 @@
         <v>999108</v>
       </c>
       <c r="K9" s="4"/>
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
       <c r="Q9" s="4" t="s">
         <v>31</v>
       </c>
